--- a/Backend/Telesale.Api/templates/manage-import-template.xlsx
+++ b/Backend/Telesale.Api/templates/manage-import-template.xlsx
@@ -1,131 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{377B6FC7-AFE5-4DEC-AD8E-EF3121DB403B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{02526A62-2978-497E-938F-0B2F780F5499}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="factory" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="TABLE" localSheetId="0">factory!$A$1:$B$1</definedName>
-    <definedName name="TABLE_2" localSheetId="0">factory!$A$1:$B$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>บริษัท สยามแปซิฟิค อีเล็คทริคไวร์ แอนด์ เคเบิ้ลจำกัด</t>
-  </si>
-  <si>
-    <t>บริษัท ทอสเท็มไทย จำกัด</t>
-  </si>
-  <si>
-    <t>บริษัท ทอสเท็ม ไทย จำกัด</t>
-  </si>
-  <si>
-    <t>บริษัท ฟูจิคูระ อิเล็กทรอนิกส์ (ประเทศไทย) จำกัด</t>
-  </si>
-  <si>
-    <t>บริษัท พานาโซนิค แมนูแฟคเจอริ่ง (ประเทศไทย) จำกัด</t>
-  </si>
-  <si>
-    <t>บริษัท กัลฟ์ เจพี ซีอาร์เอ็น จำกัด</t>
-  </si>
-  <si>
-    <t>101/104  หมู่ที่ 20 ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>59/4  ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>60/2 ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>101/2 ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>106 ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>8 ซ. นวนคร</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>company_name</t>
-  </si>
-  <si>
-    <t>contact_name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="14"/>
-      <name val="Cordia New"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Cordia New"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -133,40 +42,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -180,36 +65,36 @@
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00000000"/>
       <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00DD0806"/>
-      <rgbColor rgb="001FB714"/>
-      <rgbColor rgb="000000D4"/>
-      <rgbColor rgb="00FCF305"/>
-      <rgbColor rgb="00F20884"/>
-      <rgbColor rgb="0000ABEA"/>
-      <rgbColor rgb="00900000"/>
-      <rgbColor rgb="00006411"/>
-      <rgbColor rgb="00000090"/>
-      <rgbColor rgb="0090713A"/>
-      <rgbColor rgb="004600A5"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
       <rgbColor rgb="00008080"/>
       <rgbColor rgb="00C0C0C0"/>
       <rgbColor rgb="00808080"/>
-      <rgbColor rgb="0063AAFE"/>
-      <rgbColor rgb="00DD2D32"/>
-      <rgbColor rgb="00FFF58C"/>
-      <rgbColor rgb="004EE257"/>
-      <rgbColor rgb="006711FF"/>
-      <rgbColor rgb="00FEA746"/>
-      <rgbColor rgb="00865357"/>
-      <rgbColor rgb="00A2BD90"/>
-      <rgbColor rgb="0063AAFE"/>
-      <rgbColor rgb="00DD2D32"/>
-      <rgbColor rgb="00FFF58C"/>
-      <rgbColor rgb="004EE257"/>
-      <rgbColor rgb="006711FF"/>
-      <rgbColor rgb="00FEA746"/>
-      <rgbColor rgb="00865357"/>
-      <rgbColor rgb="00A2BD90"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
       <rgbColor rgb="0000CCFF"/>
       <rgbColor rgb="00CCFFFF"/>
       <rgbColor rgb="00CCFFCC"/>
@@ -236,14 +121,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -290,12 +167,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -322,15 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -357,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -392,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -523,148 +402,102 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB7DB8-3D1E-4D1B-BD03-6B5031826B48}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="21.3" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="2" width="29.25" customWidth="1"/>
-    <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="23.625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>contact_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>บริษัท เอ็กแซมเปิล จำกัด</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>123/45 ถนนสุขุมวิท แขวงคลองเตย เขตคลองเตย กรุงเทพมหานคร 10110</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>สมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>somchai.j@example.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0812345678</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sample Company Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>456 Ratchadapisek Road, Huai Khwang, Bangkok 10310</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jane Doe</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jane.doe@example.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>029876543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>